--- a/data/trans_orig/P1414-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1414-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de fibromialgia en 2012</t>
+          <t>Población con diagnóstico de fibromialgia en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5470</t>
+          <t>5376</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15245</t>
+          <t>14626</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35518</t>
+          <t>35026</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16239</t>
+          <t>16358</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>36831</t>
+          <t>35444</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>697999</t>
+          <t>698093</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>661532</t>
+          <t>662024</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>681805</t>
+          <t>682424</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1363688</t>
+          <t>1365075</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1384280</t>
+          <t>1384161</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,83%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>1011</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8824</t>
+          <t>8589</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13110</t>
+          <t>13018</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30834</t>
+          <t>30800</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15433</t>
+          <t>15301</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35664</t>
+          <t>35809</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1009123</t>
+          <t>1009358</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1016932</t>
+          <t>1016936</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>998139</t>
+          <t>998173</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1015863</t>
+          <t>1015955</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2011257</t>
+          <t>2011112</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2031488</t>
+          <t>2031620</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5214</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9919</t>
+          <t>9253</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27597</t>
+          <t>26786</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9572</t>
+          <t>10174</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28511</t>
+          <t>29465</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>752409</t>
+          <t>752377</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>749577</t>
+          <t>750388</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>767255</t>
+          <t>767921</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1506286</t>
+          <t>1505332</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1525225</t>
+          <t>1524623</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,34%</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6070</t>
+          <t>7254</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21685</t>
+          <t>21791</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>43926</t>
+          <t>43728</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>23362</t>
+          <t>24129</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>46346</t>
+          <t>47482</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>941669</t>
+          <t>940485</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1007008</t>
+          <t>1007206</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1029249</t>
+          <t>1029143</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1952328</t>
+          <t>1951192</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1975312</t>
+          <t>1974545</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,79%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3099</t>
+          <t>3156</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14165</t>
+          <t>14751</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>74546</t>
+          <t>74465</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>113080</t>
+          <t>113465</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>83082</t>
+          <t>81633</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>125830</t>
+          <t>122298</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3412614</t>
+          <t>3412028</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3423680</t>
+          <t>3423623</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3441052</t>
+          <t>3440667</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3479586</t>
+          <t>3479667</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6855081</t>
+          <t>6858613</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6897829</t>
+          <t>6899278</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,83%</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de fibromialgia en 2016</t>
+          <t>Población con diagnóstico de fibromialgia en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1014</t>
+          <t>1021</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8485</t>
+          <t>8545</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17068</t>
+          <t>17631</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37173</t>
+          <t>37654</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19767</t>
+          <t>19460</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>41674</t>
+          <t>38949</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>666315</t>
+          <t>666255</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>673786</t>
+          <t>673779</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>635666</t>
+          <t>635185</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>655771</t>
+          <t>655208</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1305965</t>
+          <t>1308690</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1327872</t>
+          <t>1328179</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,56%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8812</t>
+          <t>8659</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28647</t>
+          <t>29243</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>54575</t>
+          <t>54938</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>30438</t>
+          <t>31228</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>57722</t>
+          <t>59818</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1013619</t>
+          <t>1013772</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1021411</t>
+          <t>1021423</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>988338</t>
+          <t>987975</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1014266</t>
+          <t>1013670</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2007622</t>
+          <t>2005526</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2034906</t>
+          <t>2034116</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,49%</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7141</t>
+          <t>6886</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16571</t>
+          <t>16484</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36792</t>
+          <t>37046</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18661</t>
+          <t>18032</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>40127</t>
+          <t>40275</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -3478,7 +3478,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>752411</t>
+          <t>752666</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>748219</t>
+          <t>747965</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>768440</t>
+          <t>768527</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1504436</t>
+          <t>1504288</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1525902</t>
+          <t>1526531</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,83%</t>
         </is>
       </c>
     </row>
@@ -3708,12 +3708,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1966</t>
+          <t>1924</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13011</t>
+          <t>12221</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3728,7 +3728,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24602</t>
+          <t>23644</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>47756</t>
+          <t>47646</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>28265</t>
+          <t>28765</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>55086</t>
+          <t>55006</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>924556</t>
+          <t>925346</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>935601</t>
+          <t>935643</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>996023</t>
+          <t>996133</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1019177</t>
+          <t>1020135</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1926260</t>
+          <t>1926340</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1953081</t>
+          <t>1952581</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3911,7 +3911,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,55%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8184</t>
+          <t>7736</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23990</t>
+          <t>24968</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>104227</t>
+          <t>103445</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>150014</t>
+          <t>148355</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>117905</t>
+          <t>117704</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>165636</t>
+          <t>165178</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3370360</t>
+          <t>3369382</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3386166</t>
+          <t>3386614</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3394528</t>
+          <t>3396187</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3440315</t>
+          <t>3441097</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6773256</t>
+          <t>6773714</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6820987</t>
+          <t>6821188</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -4431,7 +4431,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de fibromialgia en 2023</t>
+          <t>Población con diagnóstico de fibromialgia en 2023 (tasa de respuesta: 99,61%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4626,12 +4626,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>955</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12728</t>
+          <t>12220</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4661,12 +4661,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16668</t>
+          <t>16374</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29832</t>
+          <t>29947</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18875</t>
+          <t>19320</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35117</t>
+          <t>36684</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4711,12 +4711,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>622713</t>
+          <t>623221</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>634494</t>
+          <t>634486</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4754,7 +4754,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>643261</t>
+          <t>643146</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>656425</t>
+          <t>656719</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1273417</t>
+          <t>1271850</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1289659</t>
+          <t>1289214</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,52%</t>
         </is>
       </c>
     </row>
@@ -4974,7 +4974,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5473</t>
+          <t>6475</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>35267</t>
+          <t>35229</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>55180</t>
+          <t>54972</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>29817</t>
+          <t>29931</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>57949</t>
+          <t>58521</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5059,7 +5059,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -5082,7 +5082,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1186070</t>
+          <t>1185068</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -5097,7 +5097,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>898897</t>
+          <t>899105</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>918810</t>
+          <t>918848</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2087670</t>
+          <t>2087098</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2115802</t>
+          <t>2115688</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>1091</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9109</t>
+          <t>9490</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5332,7 +5332,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11262</t>
+          <t>12206</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35866</t>
+          <t>35531</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5362,12 +5362,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17103</t>
+          <t>17648</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37924</t>
+          <t>38426</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5397,12 +5397,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>692891</t>
+          <t>692510</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>700900</t>
+          <t>700909</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5440,7 +5440,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>893717</t>
+          <t>894052</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>918321</t>
+          <t>917377</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1593659</t>
+          <t>1593157</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1614480</t>
+          <t>1613935</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,92%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1891</t>
+          <t>1546</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10775</t>
+          <t>9754</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>36894</t>
+          <t>37957</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>60264</t>
+          <t>61417</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>42543</t>
+          <t>43065</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>66581</t>
+          <t>66341</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -5768,12 +5768,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>913182</t>
+          <t>914203</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>922066</t>
+          <t>922411</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5783,12 +5783,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1028959</t>
+          <t>1027806</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1052329</t>
+          <t>1051266</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1946598</t>
+          <t>1946838</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1970636</t>
+          <t>1970114</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,86%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8432</t>
+          <t>8274</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24006</t>
+          <t>24721</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>111809</t>
+          <t>112384</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>161825</t>
+          <t>161418</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>128277</t>
+          <t>129157</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>175852</t>
+          <t>176545</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3428935</t>
+          <t>3428220</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3444509</t>
+          <t>3444667</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3484150</t>
+          <t>3484557</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3534166</t>
+          <t>3533591</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6923064</t>
+          <t>6922371</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6970639</t>
+          <t>6969759</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,18%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1414-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1414-Habitat-trans_orig.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5376</t>
+          <t>5433</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14626</t>
+          <t>15631</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35026</t>
+          <t>35260</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16358</t>
+          <t>16222</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35444</t>
+          <t>35985</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>698093</t>
+          <t>698036</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>662024</t>
+          <t>661790</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>682424</t>
+          <t>681419</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1365075</t>
+          <t>1364534</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1384161</t>
+          <t>1384297</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,84%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1011</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8589</t>
+          <t>7916</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13018</t>
+          <t>13010</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30800</t>
+          <t>31940</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15301</t>
+          <t>15101</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35809</t>
+          <t>35810</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1009358</t>
+          <t>1010031</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1016936</t>
+          <t>1016939</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>998173</t>
+          <t>997033</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1015955</t>
+          <t>1015963</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2011112</t>
+          <t>2011111</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2031620</t>
+          <t>2031820</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,26%</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>6046</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9253</t>
+          <t>9260</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26786</t>
+          <t>27544</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10174</t>
+          <t>10160</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29465</t>
+          <t>28723</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>752377</t>
+          <t>751577</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>750388</t>
+          <t>749630</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>767921</t>
+          <t>767914</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1505332</t>
+          <t>1506074</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1524623</t>
+          <t>1524637</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7254</t>
+          <t>6242</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21791</t>
+          <t>22293</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>43728</t>
+          <t>45721</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24129</t>
+          <t>23414</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>47482</t>
+          <t>46580</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>940485</t>
+          <t>941497</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1007206</t>
+          <t>1005213</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1029143</t>
+          <t>1028641</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1951192</t>
+          <t>1952094</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1974545</t>
+          <t>1975260</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,83%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3156</t>
+          <t>3101</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14751</t>
+          <t>14843</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>74465</t>
+          <t>74492</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>113465</t>
+          <t>112317</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>81633</t>
+          <t>80983</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>122298</t>
+          <t>122212</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3412028</t>
+          <t>3411936</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3423623</t>
+          <t>3423678</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3440667</t>
+          <t>3441815</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3479667</t>
+          <t>3479640</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6858613</t>
+          <t>6858699</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6899278</t>
+          <t>6899928</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,84%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1021</t>
+          <t>1017</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8545</t>
+          <t>8498</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17631</t>
+          <t>16875</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37654</t>
+          <t>37425</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19460</t>
+          <t>19599</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38949</t>
+          <t>41210</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>666255</t>
+          <t>666302</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>673779</t>
+          <t>673783</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>635185</t>
+          <t>635414</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>655208</t>
+          <t>655964</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1308690</t>
+          <t>1306429</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1328179</t>
+          <t>1328040</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,55%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8659</t>
+          <t>8658</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29243</t>
+          <t>27046</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>54938</t>
+          <t>54117</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3072,47 +3072,47 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
+          <t>2,59%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>5,19%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>43225</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>31336</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>57773</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>2,09%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
           <t>2,8%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>5,27%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>43225</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>31228</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>59818</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>2,09%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>1,51%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1013772</t>
+          <t>1013773</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1021423</t>
+          <t>1021416</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>987975</t>
+          <t>988796</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1013670</t>
+          <t>1015867</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3185,47 +3185,47 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
+          <t>97,41%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>1889</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>2022119</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>2007571</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>2034008</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>97,91%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
           <t>97,2%</t>
         </is>
       </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1889</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>2022119</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>2005526</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>2034116</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>97,91%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>97,1%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,48%</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6886</t>
+          <t>7059</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16484</t>
+          <t>16715</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37046</t>
+          <t>37044</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18032</t>
+          <t>17943</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>40275</t>
+          <t>39622</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -3478,7 +3478,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>752666</t>
+          <t>752493</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>747965</t>
+          <t>747967</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>768527</t>
+          <t>768296</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1504288</t>
+          <t>1504941</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1526531</t>
+          <t>1526620</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,84%</t>
         </is>
       </c>
     </row>
@@ -3708,12 +3708,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1924</t>
+          <t>1943</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12221</t>
+          <t>12769</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3728,7 +3728,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23644</t>
+          <t>24149</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>47646</t>
+          <t>48592</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>28765</t>
+          <t>27458</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>55006</t>
+          <t>53833</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -3821,12 +3821,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>925346</t>
+          <t>924798</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>935643</t>
+          <t>935624</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>996133</t>
+          <t>995187</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1020135</t>
+          <t>1019630</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1926340</t>
+          <t>1927513</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1952581</t>
+          <t>1953888</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,61%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7736</t>
+          <t>7964</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24968</t>
+          <t>23343</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>103445</t>
+          <t>104683</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>148355</t>
+          <t>152413</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>117704</t>
+          <t>118219</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>165178</t>
+          <t>163638</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3369382</t>
+          <t>3371007</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3386614</t>
+          <t>3386386</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3396187</t>
+          <t>3392129</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3441097</t>
+          <t>3439859</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6773714</t>
+          <t>6775254</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6821188</t>
+          <t>6820673</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -4621,32 +4621,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4236</t>
+          <t>4422</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>958</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12220</t>
+          <t>12879</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4656,22 +4656,22 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>22377</t>
+          <t>23676</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16374</t>
+          <t>17727</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29947</t>
+          <t>31851</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4691,22 +4691,22 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>26613</t>
+          <t>28098</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19320</t>
+          <t>20976</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>36684</t>
+          <t>39112</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -4734,32 +4734,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>631205</t>
+          <t>686288</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>623221</t>
+          <t>677831</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>634486</t>
+          <t>689752</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4769,27 +4769,27 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>650716</t>
+          <t>706645</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>643146</t>
+          <t>698470</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>656719</t>
+          <t>712594</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4804,27 +4804,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1281921</t>
+          <t>1392932</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1271850</t>
+          <t>1381918</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1289214</t>
+          <t>1400054</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4847,17 +4847,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4882,17 +4882,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>673093</t>
+          <t>730321</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>673093</t>
+          <t>730321</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>673093</t>
+          <t>730321</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1308534</t>
+          <t>1421030</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1308534</t>
+          <t>1421030</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1308534</t>
+          <t>1421030</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1698</t>
+          <t>1649</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6475</t>
+          <t>5510</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4999,32 +4999,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>43891</t>
+          <t>47987</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>35229</t>
+          <t>38631</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>54972</t>
+          <t>60827</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5034,32 +5034,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>45589</t>
+          <t>49636</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>29931</t>
+          <t>39482</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>58521</t>
+          <t>61694</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -5077,27 +5077,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1189845</t>
+          <t>1045870</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1185068</t>
+          <t>1042009</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1191543</t>
+          <t>1047519</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,84%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -5112,32 +5112,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>910186</t>
+          <t>1018107</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>899105</t>
+          <t>1005267</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>918848</t>
+          <t>1027463</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5147,32 +5147,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2100030</t>
+          <t>2063977</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2087098</t>
+          <t>2051919</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2115688</t>
+          <t>2074131</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,13%</t>
         </is>
       </c>
     </row>
@@ -5190,17 +5190,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1191543</t>
+          <t>1047519</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1191543</t>
+          <t>1047519</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1191543</t>
+          <t>1047519</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5225,17 +5225,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>954077</t>
+          <t>1066094</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>954077</t>
+          <t>1066094</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>954077</t>
+          <t>1066094</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5260,17 +5260,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2145619</t>
+          <t>2113613</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2145619</t>
+          <t>2113613</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2145619</t>
+          <t>2113613</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5307,32 +5307,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3614</t>
+          <t>3903</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1091</t>
+          <t>1114</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9490</t>
+          <t>9698</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5342,67 +5342,67 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>24172</t>
+          <t>27249</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12206</t>
+          <t>19722</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35531</t>
+          <t>35838</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
+          <t>3,38%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>2,45%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>4,45%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>31152</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>22848</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>41701</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>1,94%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
           <t>2,6%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>3,82%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>27786</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>17648</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>38426</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>1,7%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -5420,32 +5420,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>698386</t>
+          <t>796124</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>692510</t>
+          <t>790329</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>700909</t>
+          <t>798913</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5455,67 +5455,67 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>905411</t>
+          <t>778306</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>894052</t>
+          <t>769717</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>917377</t>
+          <t>785833</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
+          <t>96,62%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>95,55%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>97,55%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>1665</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>1574429</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>1563880</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>1582733</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>98,06%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
           <t>97,4%</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>96,18%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>98,69%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>1665</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>1603797</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>1593157</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>1613935</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>98,3%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>97,64%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,58%</t>
         </is>
       </c>
     </row>
@@ -5533,17 +5533,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>702000</t>
+          <t>800027</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>702000</t>
+          <t>800027</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>702000</t>
+          <t>800027</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5568,17 +5568,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>929583</t>
+          <t>805555</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>929583</t>
+          <t>805555</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>929583</t>
+          <t>805555</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5603,17 +5603,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1631583</t>
+          <t>1605581</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1631583</t>
+          <t>1605581</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1631583</t>
+          <t>1605581</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5650,27 +5650,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4757</t>
+          <t>4793</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1546</t>
+          <t>1831</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9754</t>
+          <t>10435</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>49170</t>
+          <t>56030</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37957</t>
+          <t>44434</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>61417</t>
+          <t>68364</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>53928</t>
+          <t>60823</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>43065</t>
+          <t>48623</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>66341</t>
+          <t>75391</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -5763,22 +5763,22 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>919200</t>
+          <t>982195</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>914203</t>
+          <t>976553</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>922411</t>
+          <t>985157</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -5788,7 +5788,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5798,32 +5798,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1040053</t>
+          <t>1058261</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1027806</t>
+          <t>1045927</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1051266</t>
+          <t>1069857</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5833,32 +5833,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1959251</t>
+          <t>2040456</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1946838</t>
+          <t>2025888</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1970114</t>
+          <t>2052656</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,69%</t>
         </is>
       </c>
     </row>
@@ -5876,17 +5876,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>923957</t>
+          <t>986988</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>923957</t>
+          <t>986988</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>923957</t>
+          <t>986988</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5911,17 +5911,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1089223</t>
+          <t>1114291</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1089223</t>
+          <t>1114291</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1089223</t>
+          <t>1114291</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5946,17 +5946,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2013179</t>
+          <t>2101279</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2013179</t>
+          <t>2101279</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2013179</t>
+          <t>2101279</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>14305</t>
+          <t>14767</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8274</t>
+          <t>8751</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24721</t>
+          <t>24926</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>139611</t>
+          <t>154942</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>112384</t>
+          <t>137214</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>161418</t>
+          <t>175174</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>153915</t>
+          <t>169709</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>129157</t>
+          <t>149484</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>176545</t>
+          <t>190076</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -6106,32 +6106,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3438636</t>
+          <t>3510476</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3428220</t>
+          <t>3500317</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3444667</t>
+          <t>3516492</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6141,32 +6141,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3506364</t>
+          <t>3561318</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3484557</t>
+          <t>3541086</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3533591</t>
+          <t>3579046</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6176,32 +6176,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6945001</t>
+          <t>7071794</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6922371</t>
+          <t>7051427</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6969759</t>
+          <t>7092019</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>97,94%</t>
         </is>
       </c>
     </row>
@@ -6219,17 +6219,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3452941</t>
+          <t>3525243</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3452941</t>
+          <t>3525243</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3452941</t>
+          <t>3525243</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6254,17 +6254,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3645975</t>
+          <t>3716260</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3645975</t>
+          <t>3716260</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3645975</t>
+          <t>3716260</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6289,17 +6289,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7098916</t>
+          <t>7241503</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7098916</t>
+          <t>7241503</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7098916</t>
+          <t>7241503</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
